--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/130.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/130.xlsx
@@ -426,13 +426,13 @@
         <v>-28.48906941868561</v>
       </c>
       <c r="E2">
-        <v>-5.853860799994904</v>
+        <v>-6.682200208529951</v>
       </c>
       <c r="F2">
-        <v>-1.59200834687751</v>
+        <v>-1.640270200944612</v>
       </c>
       <c r="G2">
-        <v>-10.87315029875954</v>
+        <v>-11.15303375028615</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-27.69148429147387</v>
       </c>
       <c r="E3">
-        <v>-5.524473186098986</v>
+        <v>-7.197934527841505</v>
       </c>
       <c r="F3">
-        <v>-1.25750511009501</v>
+        <v>-2.086381944705877</v>
       </c>
       <c r="G3">
-        <v>-11.71349255735706</v>
+        <v>-10.69134506937939</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-26.61063196663006</v>
       </c>
       <c r="E4">
-        <v>-6.974780385691525</v>
+        <v>-7.62491075660272</v>
       </c>
       <c r="F4">
-        <v>-1.440198257088274</v>
+        <v>-1.575496629003139</v>
       </c>
       <c r="G4">
-        <v>-10.55494728261587</v>
+        <v>-10.5827095175082</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-25.35252495127715</v>
       </c>
       <c r="E5">
-        <v>-7.33445896222475</v>
+        <v>-7.83618671143058</v>
       </c>
       <c r="F5">
-        <v>-1.180726255461548</v>
+        <v>-1.692937924868466</v>
       </c>
       <c r="G5">
-        <v>-10.46203020096515</v>
+        <v>-10.21919506456853</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-23.94391627269168</v>
       </c>
       <c r="E6">
-        <v>-8.425123813076125</v>
+        <v>-9.377122261338627</v>
       </c>
       <c r="F6">
-        <v>-0.8999407396248377</v>
+        <v>-1.977452276283079</v>
       </c>
       <c r="G6">
-        <v>-9.944813739728195</v>
+        <v>-9.752411454076832</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-22.44602036677108</v>
       </c>
       <c r="E7">
-        <v>-9.271952980984491</v>
+        <v>-8.937593102628149</v>
       </c>
       <c r="F7">
-        <v>-0.934650822173524</v>
+        <v>-1.738385533523832</v>
       </c>
       <c r="G7">
-        <v>-9.581901806076669</v>
+        <v>-9.610240075892831</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-20.92948879754983</v>
       </c>
       <c r="E8">
-        <v>-10.17316006477696</v>
+        <v>-10.35764556737544</v>
       </c>
       <c r="F8">
-        <v>-0.8664556536017437</v>
+        <v>-1.945037775458822</v>
       </c>
       <c r="G8">
-        <v>-9.702799618625313</v>
+        <v>-8.517783221752113</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-19.48132494631571</v>
       </c>
       <c r="E9">
-        <v>-10.82724379349685</v>
+        <v>-10.75734226871445</v>
       </c>
       <c r="F9">
-        <v>-0.8076558203733079</v>
+        <v>-1.115650987543183</v>
       </c>
       <c r="G9">
-        <v>-9.013328851889</v>
+        <v>-8.571119420935311</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-18.1558265618656</v>
       </c>
       <c r="E10">
-        <v>-10.67042273861123</v>
+        <v>-11.06456300234282</v>
       </c>
       <c r="F10">
-        <v>-0.7289844371708957</v>
+        <v>-1.478516021712331</v>
       </c>
       <c r="G10">
-        <v>-8.591270711632855</v>
+        <v>-7.292785366401136</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-17.01624858726716</v>
       </c>
       <c r="E11">
-        <v>-12.17431084266252</v>
+        <v>-13.85299351493589</v>
       </c>
       <c r="F11">
-        <v>-0.5303346612266217</v>
+        <v>-1.495666764923582</v>
       </c>
       <c r="G11">
-        <v>-7.7054879049633</v>
+        <v>-7.660037425254646</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-16.09455706110756</v>
       </c>
       <c r="E12">
-        <v>-11.01815972918623</v>
+        <v>-12.11183148677869</v>
       </c>
       <c r="F12">
-        <v>-0.1641177134874461</v>
+        <v>-1.126293491294936</v>
       </c>
       <c r="G12">
-        <v>-6.679000291783639</v>
+        <v>-6.836638538727116</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-15.37758087016866</v>
       </c>
       <c r="E13">
-        <v>-13.07817614069749</v>
+        <v>-13.42966723622485</v>
       </c>
       <c r="F13">
-        <v>-0.3469890273961969</v>
+        <v>-0.8010723548828261</v>
       </c>
       <c r="G13">
-        <v>-6.629471219970603</v>
+        <v>-6.440458932951454</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-14.84740692487386</v>
       </c>
       <c r="E14">
-        <v>-14.23150601486701</v>
+        <v>-14.33665265285111</v>
       </c>
       <c r="F14">
-        <v>0.005364158759221757</v>
+        <v>-0.6651080346305187</v>
       </c>
       <c r="G14">
-        <v>-5.958542818799748</v>
+        <v>-5.013279440426106</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-14.46845548861445</v>
       </c>
       <c r="E15">
-        <v>-14.96050428909579</v>
+        <v>-14.55799087692401</v>
       </c>
       <c r="F15">
-        <v>0.2393084047349792</v>
+        <v>-0.3742390632302057</v>
       </c>
       <c r="G15">
-        <v>-4.841220457113565</v>
+        <v>-5.503452055152755</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-14.18680749838026</v>
       </c>
       <c r="E16">
-        <v>-16.33381837360992</v>
+        <v>-16.45959221069896</v>
       </c>
       <c r="F16">
-        <v>0.7441993935477791</v>
+        <v>-0.4404062963772658</v>
       </c>
       <c r="G16">
-        <v>-5.130714422340673</v>
+        <v>-4.875557435446885</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-13.96865049098198</v>
       </c>
       <c r="E17">
-        <v>-16.60467093248269</v>
+        <v>-17.13246457807668</v>
       </c>
       <c r="F17">
-        <v>0.564510536676104</v>
+        <v>-0.1845768183560506</v>
       </c>
       <c r="G17">
-        <v>-4.18981765353333</v>
+        <v>-3.267466560836985</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-13.78782475425762</v>
       </c>
       <c r="E18">
-        <v>-17.86511280235564</v>
+        <v>-18.05913074274027</v>
       </c>
       <c r="F18">
-        <v>0.6163388964647754</v>
+        <v>0.2646817490591923</v>
       </c>
       <c r="G18">
-        <v>-3.261325498861637</v>
+        <v>-3.902141177807282</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-13.61873136929053</v>
       </c>
       <c r="E19">
-        <v>-19.17699813695572</v>
+        <v>-19.1668362412825</v>
       </c>
       <c r="F19">
-        <v>0.9406026826510021</v>
+        <v>0.3032283591880308</v>
       </c>
       <c r="G19">
-        <v>-2.404761567121688</v>
+        <v>-2.873253419111651</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-13.4541120597434</v>
       </c>
       <c r="E20">
-        <v>-19.67391211829139</v>
+        <v>-19.87177020463453</v>
       </c>
       <c r="F20">
-        <v>1.22564282442954</v>
+        <v>0.7839409097898166</v>
       </c>
       <c r="G20">
-        <v>-2.612786317172872</v>
+        <v>-2.735435408311791</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-13.29435983523827</v>
       </c>
       <c r="E21">
-        <v>-19.86852781724503</v>
+        <v>-19.56675483784789</v>
       </c>
       <c r="F21">
-        <v>1.37363539110961</v>
+        <v>0.4099107489168205</v>
       </c>
       <c r="G21">
-        <v>-2.995895889159491</v>
+        <v>-2.998554257227526</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-13.13700774838345</v>
       </c>
       <c r="E22">
-        <v>-21.63220088969436</v>
+        <v>-21.32625265726214</v>
       </c>
       <c r="F22">
-        <v>1.602001032998232</v>
+        <v>1.111414867866639</v>
       </c>
       <c r="G22">
-        <v>-1.987752008812933</v>
+        <v>-2.857438943070552</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-12.9858481901463</v>
       </c>
       <c r="E23">
-        <v>-21.24224946441985</v>
+        <v>-21.00014365854777</v>
       </c>
       <c r="F23">
-        <v>1.80261856354244</v>
+        <v>1.014270347013583</v>
       </c>
       <c r="G23">
-        <v>-1.757632677832653</v>
+        <v>-3.239667909943725</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-12.84837972427267</v>
       </c>
       <c r="E24">
-        <v>-22.06206175639846</v>
+        <v>-21.33959354168874</v>
       </c>
       <c r="F24">
-        <v>1.305862280164295</v>
+        <v>0.6048760330488245</v>
       </c>
       <c r="G24">
-        <v>-1.351259902341576</v>
+        <v>-1.975022961214435</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-12.72873500447947</v>
       </c>
       <c r="E25">
-        <v>-22.57331741491642</v>
+        <v>-22.89125704652095</v>
       </c>
       <c r="F25">
-        <v>1.484067204593203</v>
+        <v>0.767909054807823</v>
       </c>
       <c r="G25">
-        <v>-1.267066108186831</v>
+        <v>-1.657376116721365</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-12.63221864686518</v>
       </c>
       <c r="E26">
-        <v>-22.06028206611344</v>
+        <v>-21.95374518660899</v>
       </c>
       <c r="F26">
-        <v>1.536538548983543</v>
+        <v>0.5975513931899171</v>
       </c>
       <c r="G26">
-        <v>-1.649639371796088</v>
+        <v>-1.029620539928144</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-12.56543885452357</v>
       </c>
       <c r="E27">
-        <v>-23.46579812929611</v>
+        <v>-23.32789251034053</v>
       </c>
       <c r="F27">
-        <v>1.143424731829501</v>
+        <v>0.7184451679509027</v>
       </c>
       <c r="G27">
-        <v>-1.208734295784873</v>
+        <v>-1.606161977228839</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-12.5288308831901</v>
       </c>
       <c r="E28">
-        <v>-23.51093795820457</v>
+        <v>-22.76442354651412</v>
       </c>
       <c r="F28">
-        <v>1.123070943404274</v>
+        <v>0.5130891893077005</v>
       </c>
       <c r="G28">
-        <v>-2.157314840788864</v>
+        <v>-2.779240546887427</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-12.51859397366358</v>
       </c>
       <c r="E29">
-        <v>-22.82058568115725</v>
+        <v>-22.58429896438502</v>
       </c>
       <c r="F29">
-        <v>1.136557782980156</v>
+        <v>0.5201153006015476</v>
       </c>
       <c r="G29">
-        <v>-2.248222421297251</v>
+        <v>-2.716850005654323</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-12.5306026686842</v>
       </c>
       <c r="E30">
-        <v>-22.65298232965936</v>
+        <v>-22.18686197157584</v>
       </c>
       <c r="F30">
-        <v>1.072509548347954</v>
+        <v>0.7234639319969304</v>
       </c>
       <c r="G30">
-        <v>-2.041157729452455</v>
+        <v>-2.487780117609992</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-12.55722153413224</v>
       </c>
       <c r="E31">
-        <v>-21.77931742478154</v>
+        <v>-21.69861548949085</v>
       </c>
       <c r="F31">
-        <v>1.118509870367808</v>
+        <v>0.7134517431995222</v>
       </c>
       <c r="G31">
-        <v>-1.740513846849082</v>
+        <v>-2.628842463038338</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-12.5879848623745</v>
       </c>
       <c r="E32">
-        <v>-21.19985389076004</v>
+        <v>-19.88034260593105</v>
       </c>
       <c r="F32">
-        <v>0.9133328504930504</v>
+        <v>0.4519145890590633</v>
       </c>
       <c r="G32">
-        <v>-2.243643936816438</v>
+        <v>-2.467714901096469</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-12.61750335598288</v>
       </c>
       <c r="E33">
-        <v>-21.65977023945305</v>
+        <v>-21.84680074444385</v>
       </c>
       <c r="F33">
-        <v>1.021476208928833</v>
+        <v>0.8439332735725783</v>
       </c>
       <c r="G33">
-        <v>-2.183348970909692</v>
+        <v>-2.2011199793645</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-12.64392945502594</v>
       </c>
       <c r="E34">
-        <v>-21.29371557151703</v>
+        <v>-20.89650953088224</v>
       </c>
       <c r="F34">
-        <v>1.004133045448856</v>
+        <v>0.8133107359916412</v>
       </c>
       <c r="G34">
-        <v>-2.368398534918334</v>
+        <v>-3.026495261578975</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-12.66341464726509</v>
       </c>
       <c r="E35">
-        <v>-20.48799589065029</v>
+        <v>-20.61328970949452</v>
       </c>
       <c r="F35">
-        <v>1.281074115175836</v>
+        <v>0.6448756933550787</v>
       </c>
       <c r="G35">
-        <v>-1.906891934016234</v>
+        <v>-3.690766155670356</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-12.67533895631232</v>
       </c>
       <c r="E36">
-        <v>-19.99210534444035</v>
+        <v>-19.70671638400296</v>
       </c>
       <c r="F36">
-        <v>1.299622478857463</v>
+        <v>0.8925958052362862</v>
       </c>
       <c r="G36">
-        <v>-2.471826598656244</v>
+        <v>-2.970954239066622</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-12.68151517175175</v>
       </c>
       <c r="E37">
-        <v>-19.0030594503211</v>
+        <v>-18.09019607443289</v>
       </c>
       <c r="F37">
-        <v>1.190703104523115</v>
+        <v>0.5452811794508382</v>
       </c>
       <c r="G37">
-        <v>-2.225243924709169</v>
+        <v>-2.82383359530141</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-12.67841637640287</v>
       </c>
       <c r="E38">
-        <v>-18.04075872369115</v>
+        <v>-19.50485512663704</v>
       </c>
       <c r="F38">
-        <v>1.624256852227903</v>
+        <v>0.6252409074154605</v>
       </c>
       <c r="G38">
-        <v>-2.158278209540792</v>
+        <v>-3.186709112952004</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-12.66515923896232</v>
       </c>
       <c r="E39">
-        <v>-17.94209233201203</v>
+        <v>-18.00146062625258</v>
       </c>
       <c r="F39">
-        <v>1.26258118120125</v>
+        <v>0.8796790997899621</v>
       </c>
       <c r="G39">
-        <v>-2.133131305624488</v>
+        <v>-2.27193585899505</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-12.64495084689827</v>
       </c>
       <c r="E40">
-        <v>-18.29884098586229</v>
+        <v>-17.5643496726622</v>
       </c>
       <c r="F40">
-        <v>1.470689640725486</v>
+        <v>1.317627631410094</v>
       </c>
       <c r="G40">
-        <v>-2.697662083708707</v>
+        <v>-2.87875223525238</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-12.61493421191717</v>
       </c>
       <c r="E41">
-        <v>-16.88579407040486</v>
+        <v>-17.73192585331605</v>
       </c>
       <c r="F41">
-        <v>1.719926942873684</v>
+        <v>0.9354904799559636</v>
       </c>
       <c r="G41">
-        <v>-2.634662402096376</v>
+        <v>-3.077606774159782</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-12.57593565674706</v>
       </c>
       <c r="E42">
-        <v>-16.55659665241727</v>
+        <v>-17.90408484966565</v>
       </c>
       <c r="F42">
-        <v>1.246861316284598</v>
+        <v>0.8649126258344046</v>
       </c>
       <c r="G42">
-        <v>-2.902747069321018</v>
+        <v>-3.025346502276848</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-12.53556251111123</v>
       </c>
       <c r="E43">
-        <v>-16.17336095409614</v>
+        <v>-16.26848607910126</v>
       </c>
       <c r="F43">
-        <v>1.532264126717772</v>
+        <v>0.7402860562307282</v>
       </c>
       <c r="G43">
-        <v>-2.769904808466683</v>
+        <v>-3.73635236774612</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-12.49479056884304</v>
       </c>
       <c r="E44">
-        <v>-14.74039780995298</v>
+        <v>-16.49165833514727</v>
       </c>
       <c r="F44">
-        <v>1.761909402986069</v>
+        <v>1.130858025390489</v>
       </c>
       <c r="G44">
-        <v>-2.118846301622532</v>
+        <v>-3.487366237737534</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-12.4584004232738</v>
       </c>
       <c r="E45">
-        <v>-13.86421054505288</v>
+        <v>-15.01490484734994</v>
       </c>
       <c r="F45">
-        <v>1.663144750981518</v>
+        <v>1.001865178577946</v>
       </c>
       <c r="G45">
-        <v>-2.637572371625395</v>
+        <v>-3.435218524402935</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-12.43817921954646</v>
       </c>
       <c r="E46">
-        <v>-13.55220321439841</v>
+        <v>-14.33543902181705</v>
       </c>
       <c r="F46">
-        <v>1.525637901167573</v>
+        <v>1.205372972417831</v>
       </c>
       <c r="G46">
-        <v>-2.674200247471892</v>
+        <v>-3.533958855657237</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-12.43615987666732</v>
       </c>
       <c r="E47">
-        <v>-13.15151024877771</v>
+        <v>-14.5303536000552</v>
       </c>
       <c r="F47">
-        <v>1.502621903098492</v>
+        <v>0.8774555766846851</v>
       </c>
       <c r="G47">
-        <v>-3.794803359787492</v>
+        <v>-3.783597163137059</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-12.45573553032005</v>
       </c>
       <c r="E48">
-        <v>-12.15299984398242</v>
+        <v>-14.59720746183044</v>
       </c>
       <c r="F48">
-        <v>1.744995423809175</v>
+        <v>0.8061618874893475</v>
       </c>
       <c r="G48">
-        <v>-3.510301697233605</v>
+        <v>-3.754245866385881</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-12.50448111062672</v>
       </c>
       <c r="E49">
-        <v>-11.13623968893623</v>
+        <v>-12.29636680259126</v>
       </c>
       <c r="F49">
-        <v>1.612310958507743</v>
+        <v>0.7403794948797391</v>
       </c>
       <c r="G49">
-        <v>-3.027948591070714</v>
+        <v>-4.086462421797284</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-12.57835269720019</v>
       </c>
       <c r="E50">
-        <v>-11.40770359180004</v>
+        <v>-11.78657384117777</v>
       </c>
       <c r="F50">
-        <v>1.509385911063333</v>
+        <v>0.2691177093283382</v>
       </c>
       <c r="G50">
-        <v>-4.287018581111872</v>
+        <v>-4.800603373892247</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-12.67563349512955</v>
       </c>
       <c r="E51">
-        <v>-10.63482440443693</v>
+        <v>-11.72666213005629</v>
       </c>
       <c r="F51">
-        <v>1.541448037321405</v>
+        <v>0.8092469466126235</v>
       </c>
       <c r="G51">
-        <v>-2.729860449623658</v>
+        <v>-4.242630786521324</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-12.80132460152125</v>
       </c>
       <c r="E52">
-        <v>-10.13151621780242</v>
+        <v>-11.04944695610522</v>
       </c>
       <c r="F52">
-        <v>1.390802763232974</v>
+        <v>0.7610294363111541</v>
       </c>
       <c r="G52">
-        <v>-3.51645600139111</v>
+        <v>-3.889157218202261</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-12.95120480504181</v>
       </c>
       <c r="E53">
-        <v>-10.09753454884886</v>
+        <v>-11.60039016082641</v>
       </c>
       <c r="F53">
-        <v>1.323127842054415</v>
+        <v>0.9237441331811492</v>
       </c>
       <c r="G53">
-        <v>-3.614520981355402</v>
+        <v>-3.304206995231817</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-13.12466901739747</v>
       </c>
       <c r="E54">
-        <v>-9.159692110334342</v>
+        <v>-10.09835420264425</v>
       </c>
       <c r="F54">
-        <v>1.279897421680665</v>
+        <v>0.8564397991868036</v>
       </c>
       <c r="G54">
-        <v>-3.813948244641097</v>
+        <v>-4.856647599326569</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-13.32635509946883</v>
       </c>
       <c r="E55">
-        <v>-8.781768312024212</v>
+        <v>-10.00567445360327</v>
       </c>
       <c r="F55">
-        <v>1.403074900371714</v>
+        <v>0.6942303045038336</v>
       </c>
       <c r="G55">
-        <v>-4.652377007916918</v>
+        <v>-3.974433560748347</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-13.54808186555513</v>
       </c>
       <c r="E56">
-        <v>-8.790856959357606</v>
+        <v>-10.02631070965623</v>
       </c>
       <c r="F56">
-        <v>1.216414570060275</v>
+        <v>0.8525359641052453</v>
       </c>
       <c r="G56">
-        <v>-4.450321171473041</v>
+        <v>-4.652628609377903</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-13.78301223473189</v>
       </c>
       <c r="E57">
-        <v>-8.352926351971837</v>
+        <v>-8.770560338855228</v>
       </c>
       <c r="F57">
-        <v>1.607882916768174</v>
+        <v>0.4818577168022769</v>
       </c>
       <c r="G57">
-        <v>-4.922047426454871</v>
+        <v>-4.785682745146751</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-14.02923007001743</v>
       </c>
       <c r="E58">
-        <v>-7.60897052809572</v>
+        <v>-8.609251566228002</v>
       </c>
       <c r="F58">
-        <v>0.9985488983910161</v>
+        <v>0.4062983157237031</v>
       </c>
       <c r="G58">
-        <v>-5.004374072925467</v>
+        <v>-5.719173823582745</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-14.27483418454362</v>
       </c>
       <c r="E59">
-        <v>-7.915892382439586</v>
+        <v>-8.959447518189167</v>
       </c>
       <c r="F59">
-        <v>1.285567088857938</v>
+        <v>0.3414352643980074</v>
       </c>
       <c r="G59">
-        <v>-4.810333067232165</v>
+        <v>-4.747584987080819</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-14.51211458411399</v>
       </c>
       <c r="E60">
-        <v>-7.447353819235973</v>
+        <v>-8.045334283474835</v>
       </c>
       <c r="F60">
-        <v>0.7566932495146809</v>
+        <v>0.5498042435453332</v>
       </c>
       <c r="G60">
-        <v>-4.654601694519309</v>
+        <v>-6.100608259526492</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-14.73934740918905</v>
       </c>
       <c r="E61">
-        <v>-7.614590364339239</v>
+        <v>-7.146577104120516</v>
       </c>
       <c r="F61">
-        <v>1.110261929960199</v>
+        <v>0.2356920122770732</v>
       </c>
       <c r="G61">
-        <v>-4.957605996092183</v>
+        <v>-5.525698921176658</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-14.94546848804804</v>
       </c>
       <c r="E62">
-        <v>-6.824629773019199</v>
+        <v>-8.834438993207426</v>
       </c>
       <c r="F62">
-        <v>0.8523411682776463</v>
+        <v>0.4251919272948957</v>
       </c>
       <c r="G62">
-        <v>-5.53041313802458</v>
+        <v>-5.391608584654017</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-15.12489314421543</v>
       </c>
       <c r="E63">
-        <v>-5.376998901565193</v>
+        <v>-7.953768539039741</v>
       </c>
       <c r="F63">
-        <v>0.9659103031797245</v>
+        <v>0.2119063331330882</v>
       </c>
       <c r="G63">
-        <v>-4.977144835864961</v>
+        <v>-5.678920900370746</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-15.27602710101665</v>
       </c>
       <c r="E64">
-        <v>-6.250663806443011</v>
+        <v>-5.742781861060758</v>
       </c>
       <c r="F64">
-        <v>0.6715088757350239</v>
+        <v>0.214938338108197</v>
       </c>
       <c r="G64">
-        <v>-5.248986972276676</v>
+        <v>-5.217781770023505</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-15.38767649387736</v>
       </c>
       <c r="E65">
-        <v>-5.470634158621793</v>
+        <v>-7.39133659576109</v>
       </c>
       <c r="F65">
-        <v>0.8658105870884588</v>
+        <v>0.0004158696264312032</v>
       </c>
       <c r="G65">
-        <v>-5.109616315618898</v>
+        <v>-5.879056620401847</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-15.45449333879474</v>
       </c>
       <c r="E66">
-        <v>-5.457913675134247</v>
+        <v>-6.327964857753945</v>
       </c>
       <c r="F66">
-        <v>0.500329270747005</v>
+        <v>0.0839824878134668</v>
       </c>
       <c r="G66">
-        <v>-5.680016690944245</v>
+        <v>-6.297681724933766</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-15.47651679422354</v>
       </c>
       <c r="E67">
-        <v>-5.806080870739974</v>
+        <v>-6.906667608142155</v>
       </c>
       <c r="F67">
-        <v>0.8253864935968669</v>
+        <v>-0.1763629276256239</v>
       </c>
       <c r="G67">
-        <v>-5.253171501838314</v>
+        <v>-5.79259841309824</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-15.44792984376071</v>
       </c>
       <c r="E68">
-        <v>-5.445107150640554</v>
+        <v>-5.724133605097172</v>
       </c>
       <c r="F68">
-        <v>0.4214480465107969</v>
+        <v>-0.2396201011530641</v>
       </c>
       <c r="G68">
-        <v>-6.015249153341924</v>
+        <v>-6.719206867358088</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-15.369138909887</v>
       </c>
       <c r="E69">
-        <v>-4.908392411251464</v>
+        <v>-7.085315907744751</v>
       </c>
       <c r="F69">
-        <v>0.6235764324983336</v>
+        <v>0.1535372679136519</v>
       </c>
       <c r="G69">
-        <v>-6.128373804964359</v>
+        <v>-6.09130562656114</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-15.24536865120332</v>
       </c>
       <c r="E70">
-        <v>-5.18428969016878</v>
+        <v>-6.479111734707958</v>
       </c>
       <c r="F70">
-        <v>0.3094610338182427</v>
+        <v>-0.03188935548966036</v>
       </c>
       <c r="G70">
-        <v>-6.208224163371581</v>
+        <v>-5.770470726713752</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-15.07638722675017</v>
       </c>
       <c r="E71">
-        <v>-6.264987369729273</v>
+        <v>-7.023411668059897</v>
       </c>
       <c r="F71">
-        <v>0.3827691969380193</v>
+        <v>-0.147016857012531</v>
       </c>
       <c r="G71">
-        <v>-5.946343458487533</v>
+        <v>-6.990714638670336</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-14.86627580952682</v>
       </c>
       <c r="E72">
-        <v>-5.94793079055624</v>
+        <v>-7.003318828887863</v>
       </c>
       <c r="F72">
-        <v>0.2537977301553347</v>
+        <v>-0.7277887392047389</v>
       </c>
       <c r="G72">
-        <v>-5.751335773496764</v>
+        <v>-6.04465341882173</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-14.62259884119232</v>
       </c>
       <c r="E73">
-        <v>-4.93660480431925</v>
+        <v>-6.498547945148879</v>
       </c>
       <c r="F73">
-        <v>0.3109417988491786</v>
+        <v>-0.03708945386300579</v>
       </c>
       <c r="G73">
-        <v>-5.592545456705621</v>
+        <v>-6.554960771518227</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-14.3474440104623</v>
       </c>
       <c r="E74">
-        <v>-5.8898123551418</v>
+        <v>-7.325397485735403</v>
       </c>
       <c r="F74">
-        <v>0.2351836426782172</v>
+        <v>-0.4398424970713694</v>
       </c>
       <c r="G74">
-        <v>-5.988619125024027</v>
+        <v>-5.42471072950119</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-14.04634204956108</v>
       </c>
       <c r="E75">
-        <v>-6.736120748539282</v>
+        <v>-7.762408812897615</v>
       </c>
       <c r="F75">
-        <v>0.2544533844043266</v>
+        <v>-0.340484747201487</v>
       </c>
       <c r="G75">
-        <v>-5.090623715860099</v>
+        <v>-4.932912636914759</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-13.72986834869648</v>
       </c>
       <c r="E76">
-        <v>-6.351227628731348</v>
+        <v>-7.635099823119978</v>
       </c>
       <c r="F76">
-        <v>-0.3541228306922938</v>
+        <v>-0.6913405394138576</v>
       </c>
       <c r="G76">
-        <v>-5.295271709461226</v>
+        <v>-6.586010378131051</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-13.40621860440653</v>
       </c>
       <c r="E77">
-        <v>-6.98561702399188</v>
+        <v>-8.642205271581819</v>
       </c>
       <c r="F77">
-        <v>-0.3872563340021603</v>
+        <v>-0.4588263798797421</v>
       </c>
       <c r="G77">
-        <v>-5.228809197214818</v>
+        <v>-5.22820667792667</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-13.08577882494668</v>
       </c>
       <c r="E78">
-        <v>-7.235996351875974</v>
+        <v>-8.776841332303867</v>
       </c>
       <c r="F78">
-        <v>0.1043711177688342</v>
+        <v>-0.3624388704542664</v>
       </c>
       <c r="G78">
-        <v>-5.341324708458028</v>
+        <v>-5.209104830165075</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-12.7816833039845</v>
       </c>
       <c r="E79">
-        <v>-7.037454465957683</v>
+        <v>-7.904820263490832</v>
       </c>
       <c r="F79">
-        <v>-0.1422182280887495</v>
+        <v>-0.5081437739394842</v>
       </c>
       <c r="G79">
-        <v>-5.34944547666586</v>
+        <v>-5.436300949434179</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-12.50205937399528</v>
       </c>
       <c r="E80">
-        <v>-8.968377668932293</v>
+        <v>-8.918297274881466</v>
       </c>
       <c r="F80">
-        <v>-0.1511851709819676</v>
+        <v>-0.6382753053052281</v>
       </c>
       <c r="G80">
-        <v>-4.547022206675153</v>
+        <v>-4.438598529718481</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-12.25216450007687</v>
       </c>
       <c r="E81">
-        <v>-9.100319287619776</v>
+        <v>-10.05023916631276</v>
       </c>
       <c r="F81">
-        <v>-0.482417263196128</v>
+        <v>-1.016110319640067</v>
       </c>
       <c r="G81">
-        <v>-5.258541206703012</v>
+        <v>-5.699638294355506</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-12.03832193102073</v>
       </c>
       <c r="E82">
-        <v>-9.971185595560854</v>
+        <v>-10.19616018426192</v>
       </c>
       <c r="F82">
-        <v>-0.2264650479664663</v>
+        <v>-1.127487605555177</v>
       </c>
       <c r="G82">
-        <v>-4.969014136020511</v>
+        <v>-5.277652986101224</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-11.8636605579436</v>
       </c>
       <c r="E83">
-        <v>-11.25884812269391</v>
+        <v>-12.58812279748344</v>
       </c>
       <c r="F83">
-        <v>-0.05502254779648438</v>
+        <v>-1.140565849004876</v>
       </c>
       <c r="G83">
-        <v>-4.503882487752909</v>
+        <v>-5.608631397480941</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-11.72790961043276</v>
       </c>
       <c r="E84">
-        <v>-12.09551086645505</v>
+        <v>-11.53814175711697</v>
       </c>
       <c r="F84">
-        <v>-0.158340354307923</v>
+        <v>-0.9183869542749186</v>
       </c>
       <c r="G84">
-        <v>-4.403473641546814</v>
+        <v>-4.917955592168331</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-11.63340129118124</v>
       </c>
       <c r="E85">
-        <v>-13.03692174248762</v>
+        <v>-14.92700716686106</v>
       </c>
       <c r="F85">
-        <v>-0.3791208367145478</v>
+        <v>-0.7086227302160907</v>
       </c>
       <c r="G85">
-        <v>-4.234807967412026</v>
+        <v>-4.78210073487326</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-11.58314234774855</v>
       </c>
       <c r="E86">
-        <v>-14.1976103869196</v>
+        <v>-13.89254973539289</v>
       </c>
       <c r="F86">
-        <v>-0.1254539091208652</v>
+        <v>-0.9044812244844026</v>
       </c>
       <c r="G86">
-        <v>-4.300581886186266</v>
+        <v>-4.215288990912483</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-11.57539825435218</v>
       </c>
       <c r="E87">
-        <v>-15.17521735569548</v>
+        <v>-16.59966244023021</v>
       </c>
       <c r="F87">
-        <v>-0.5077676437845673</v>
+        <v>-0.7652806011938946</v>
       </c>
       <c r="G87">
-        <v>-4.016272235273656</v>
+        <v>-3.987463867990918</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-11.6097267333882</v>
       </c>
       <c r="E88">
-        <v>-16.25956045683214</v>
+        <v>-17.59348587442755</v>
       </c>
       <c r="F88">
-        <v>-0.1205974749311701</v>
+        <v>-0.790876456199227</v>
       </c>
       <c r="G88">
-        <v>-3.740464065305895</v>
+        <v>-5.028547676453225</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-11.68557273902914</v>
       </c>
       <c r="E89">
-        <v>-18.73877770723346</v>
+        <v>-18.87314658798905</v>
       </c>
       <c r="F89">
-        <v>-0.3445683329044477</v>
+        <v>-0.4147225456936266</v>
       </c>
       <c r="G89">
-        <v>-3.685800337361449</v>
+        <v>-4.995015160685947</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-11.79305990842653</v>
       </c>
       <c r="E90">
-        <v>-19.43044777021701</v>
+        <v>-19.81036409709052</v>
       </c>
       <c r="F90">
-        <v>-0.2919972150414352</v>
+        <v>-1.119719528039947</v>
       </c>
       <c r="G90">
-        <v>-3.470270580572738</v>
+        <v>-3.989443574223403</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-11.92145462392471</v>
       </c>
       <c r="E91">
-        <v>-22.04220892634883</v>
+        <v>-22.91632667862741</v>
       </c>
       <c r="F91">
-        <v>-0.1946721517140194</v>
+        <v>-0.8708361841638492</v>
       </c>
       <c r="G91">
-        <v>-3.897552761689852</v>
+        <v>-4.521756123119435</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-12.06105898971437</v>
       </c>
       <c r="E92">
-        <v>-23.7766280567086</v>
+        <v>-24.2811725167472</v>
       </c>
       <c r="F92">
-        <v>-0.4133470971060674</v>
+        <v>-1.386360174492909</v>
       </c>
       <c r="G92">
-        <v>-3.3217230916801</v>
+        <v>-3.315989226806083</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-12.19354110000197</v>
       </c>
       <c r="E93">
-        <v>-26.78900066592897</v>
+        <v>-26.70050522687108</v>
       </c>
       <c r="F93">
-        <v>-0.3450672002678111</v>
+        <v>-1.143028511703385</v>
       </c>
       <c r="G93">
-        <v>-3.793167950291092</v>
+        <v>-4.247331761187088</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-12.3036916189746</v>
       </c>
       <c r="E94">
-        <v>-28.74380251234603</v>
+        <v>-28.96150890026478</v>
       </c>
       <c r="F94">
-        <v>-0.4450204235618986</v>
+        <v>-1.30212127314477</v>
       </c>
       <c r="G94">
-        <v>-3.752199949242612</v>
+        <v>-4.908633095929744</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-12.38438084878654</v>
       </c>
       <c r="E95">
-        <v>-31.62883896094472</v>
+        <v>-31.03295518017141</v>
       </c>
       <c r="F95">
-        <v>-0.3554380984550663</v>
+        <v>-1.414852627617581</v>
       </c>
       <c r="G95">
-        <v>-3.722928105584375</v>
+        <v>-4.175009583336171</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-12.42729000532505</v>
       </c>
       <c r="E96">
-        <v>-33.3634369660278</v>
+        <v>-32.99224021585606</v>
       </c>
       <c r="F96">
-        <v>-0.548700898727973</v>
+        <v>-1.293291320813237</v>
       </c>
       <c r="G96">
-        <v>-4.064331424867256</v>
+        <v>-4.676894908180761</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-12.42944454962504</v>
       </c>
       <c r="E97">
-        <v>-35.38543004553366</v>
+        <v>-35.89969034655572</v>
       </c>
       <c r="F97">
-        <v>-0.8033315113712005</v>
+        <v>-1.149227136656415</v>
       </c>
       <c r="G97">
-        <v>-4.306911649257352</v>
+        <v>-4.768275896701264</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-12.40568125466918</v>
       </c>
       <c r="E98">
-        <v>-39.58283184697724</v>
+        <v>-37.64635447063223</v>
       </c>
       <c r="F98">
-        <v>-0.4657685547600708</v>
+        <v>-1.17584289827129</v>
       </c>
       <c r="G98">
-        <v>-4.645679774290973</v>
+        <v>-4.5249143835639</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-12.3562458248353</v>
       </c>
       <c r="E99">
-        <v>-41.69427587355662</v>
+        <v>-41.59044475727175</v>
       </c>
       <c r="F99">
-        <v>-0.4719022477705678</v>
+        <v>-1.421596839258479</v>
       </c>
       <c r="G99">
-        <v>-4.649755055849815</v>
+        <v>-5.62067185160727</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-12.30467924333129</v>
       </c>
       <c r="E100">
-        <v>-43.76849810802995</v>
+        <v>-44.41012400475474</v>
       </c>
       <c r="F100">
-        <v>-0.510559717313487</v>
+        <v>-1.738579537498474</v>
       </c>
       <c r="G100">
-        <v>-5.191287474072718</v>
+        <v>-4.669684539996228</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-12.25318615490492</v>
       </c>
       <c r="E101">
-        <v>-46.24942259313216</v>
+        <v>-46.20164266387723</v>
       </c>
       <c r="F101">
-        <v>-0.6553927906922554</v>
+        <v>-1.780672065171981</v>
       </c>
       <c r="G101">
-        <v>-5.077964189717926</v>
+        <v>-5.440270293535765</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-12.24133676232434</v>
       </c>
       <c r="E102">
-        <v>-49.72909862427056</v>
+        <v>-49.42239979727157</v>
       </c>
       <c r="F102">
-        <v>-0.964833089509969</v>
+        <v>-1.572341886819583</v>
       </c>
       <c r="G102">
-        <v>-5.127135722612721</v>
+        <v>-6.026584461268389</v>
       </c>
     </row>
   </sheetData>
